--- a/Test_Cases/01_Login/Login_Test_Cases.xlsx
+++ b/Test_Cases/01_Login/Login_Test_Cases.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="344">
   <si>
     <t>Application URL:</t>
   </si>
@@ -1087,6 +1087,38 @@
     <t>User is logged in and Dashboard is accessible.</t>
   </si>
   <si>
+    <t>TC-LOGIN-043</t>
+  </si>
+  <si>
+    <t>Complete flow: guest to PIN login to persistence to sign-out in one run</t>
+  </si>
+  <si>
+    <t>End-to-end PIN login lifecycle</t>
+  </si>
+  <si>
+    <t>App loaded in Guest Mode</t>
+  </si>
+  <si>
+    <t>Valid PIN, invalid PIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open app, confirm Guest Mode.
+2. Open Sign In modal.
+3. Enter invalid PIN, confirm error banner.
+4. Clear all 5 PIN boxes, enter valid PIN.
+5. Confirm Welcome Back / Dashboard.
+6. Refresh the page.
+7. Confirm session persists (not Guest Mode).
+8. Sign out.
+9. Confirm back to Guest Mode.</t>
+  </si>
+  <si>
+    <t>Each step's outcome matches the individually-tested behavior (TC-LOGIN-009, TC-LOGIN-010, TC-LOGIN-035) when chained together in one continuous session.</t>
+  </si>
+  <si>
+    <t>Signed out, Guest Mode active. NOTE: Password login deliberately excluded -- confirmed live 2026-08-23 that Password-based login is currently rejected by the server for this account (HTTP 400 on /sso/token, reproduced even via the pre-existing standalone TC-LOGIN-025). See MODULE_COVERAGE.md.</t>
+  </si>
+  <si>
     <t>Execution Status</t>
   </si>
   <si>
@@ -1121,6 +1153,21 @@
   </si>
   <si>
     <t>Script ready in login-inactivity.spec.js; requires ~15-20 min real-time run (RUN_INACTIVITY_TESTS=1), not yet executed live.</t>
+  </si>
+  <si>
+    <t>Automated - Passing</t>
+  </si>
+  <si>
+    <t>Passes live (isolated run, 2026-08-23)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Claude</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
   </si>
 </sst>
 </file>
@@ -1184,7 +1231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1192,6 +1239,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1502,7 +1552,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -3031,6 +3081,41 @@
         <v>318</v>
       </c>
     </row>
+    <row r="46" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>326</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K43"/>
   <hyperlinks>
@@ -3045,7 +3130,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -3067,29 +3152,29 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>324</v>
+      <c r="C3" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -3100,18 +3185,18 @@
         <v>14</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -3122,18 +3207,18 @@
         <v>25</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -3144,18 +3229,18 @@
         <v>33</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -3166,18 +3251,18 @@
         <v>41</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -3188,18 +3273,18 @@
         <v>48</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -3210,18 +3295,18 @@
         <v>55</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -3232,18 +3317,18 @@
         <v>63</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -3254,18 +3339,18 @@
         <v>71</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -3276,18 +3361,18 @@
         <v>77</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -3298,18 +3383,18 @@
         <v>85</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -3320,18 +3405,18 @@
         <v>93</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -3342,18 +3427,18 @@
         <v>100</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -3364,18 +3449,18 @@
         <v>107</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -3386,18 +3471,18 @@
         <v>115</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -3408,18 +3493,18 @@
         <v>122</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -3430,18 +3515,18 @@
         <v>130</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -3452,18 +3537,18 @@
         <v>138</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -3474,18 +3559,18 @@
         <v>145</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -3496,18 +3581,18 @@
         <v>153</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -3518,18 +3603,18 @@
         <v>160</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -3540,18 +3625,18 @@
         <v>168</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -3562,18 +3647,18 @@
         <v>175</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -3584,18 +3669,18 @@
         <v>181</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -3606,18 +3691,18 @@
         <v>188</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -3628,18 +3713,18 @@
         <v>195</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -3650,18 +3735,18 @@
         <v>200</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -3672,18 +3757,18 @@
         <v>206</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -3694,18 +3779,18 @@
         <v>214</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -3716,18 +3801,18 @@
         <v>221</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -3738,16 +3823,16 @@
         <v>229</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -3758,16 +3843,16 @@
         <v>236</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -3778,16 +3863,16 @@
         <v>244</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -3798,16 +3883,16 @@
         <v>251</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -3818,16 +3903,16 @@
         <v>257</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -3838,18 +3923,18 @@
         <v>263</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -3860,18 +3945,18 @@
         <v>269</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -3882,18 +3967,18 @@
         <v>277</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -3904,18 +3989,18 @@
         <v>285</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -3926,18 +4011,18 @@
         <v>291</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -3948,18 +4033,18 @@
         <v>298</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -3970,18 +4055,18 @@
         <v>305</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -3992,18 +4077,47 @@
         <v>312</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
